--- a/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10857\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1AF9BB-4720-4BD9-AA0C-D2E7E005F7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630295BE-2A2E-479D-B1D1-AF122F9D087B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -83,10 +83,6 @@
     <t>简要说明</t>
   </si>
   <si>
-    <t>小计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>辅机日耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,6 +124,10 @@
   </si>
   <si>
     <t>滑油（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油总日耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -139,7 +139,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -286,12 +286,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -300,9 +294,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -311,7 +302,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -321,12 +312,21 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,109 +645,111 @@
   <dimension ref="A1:U3"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="10"/>
-    <col min="2" max="20" width="10.625" style="2"/>
+    <col min="1" max="1" width="10.625" style="7"/>
+    <col min="2" max="16" width="10.625" style="2"/>
+    <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
+    <col min="18" max="20" width="10.625" style="2"/>
     <col min="21" max="21" width="20.625" style="2" customWidth="1"/>
     <col min="22" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="13"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="14"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="14"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="U1" s="11"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="8"/>
     </row>
     <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="J2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="T2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="11" t="s">
         <v>14</v>
       </c>
     </row>

--- a/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630295BE-2A2E-479D-B1D1-AF122F9D087B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A571C9FB-81F8-4053-A900-AE56AB9324C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -135,11 +135,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="180" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -275,7 +276,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -326,6 +327,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -646,7 +650,9 @@
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="7"/>
-    <col min="2" max="16" width="10.625" style="2"/>
+    <col min="2" max="4" width="10.625" style="2"/>
+    <col min="5" max="10" width="10.625" style="15"/>
+    <col min="11" max="16" width="10.625" style="2"/>
     <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
     <col min="18" max="20" width="10.625" style="2"/>
     <col min="21" max="21" width="20.625" style="2" customWidth="1"/>

--- a/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A571C9FB-81F8-4053-A900-AE56AB9324C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480C1379-988C-4729-9DFC-5CCF7BC3CF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>日期</t>
   </si>
@@ -128,6 +128,14 @@
   </si>
   <si>
     <t>柴油总日耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油库存</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -135,12 +143,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="180" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -276,7 +283,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -299,10 +306,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -323,13 +326,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -646,59 +649,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B800CC8-A909-447B-A086-099E135E3E25}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="7"/>
+    <col min="1" max="1" width="10.625" style="6"/>
     <col min="2" max="4" width="10.625" style="2"/>
-    <col min="5" max="10" width="10.625" style="15"/>
+    <col min="5" max="10" width="10.625" style="14"/>
     <col min="11" max="16" width="10.625" style="2"/>
     <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
-    <col min="18" max="20" width="10.625" style="2"/>
-    <col min="21" max="21" width="20.625" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="10.625" style="2"/>
+    <col min="18" max="22" width="10.625" style="2"/>
+    <col min="23" max="23" width="20.625" style="2" customWidth="1"/>
+    <col min="24" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="10"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="11" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="13"/>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="14"/>
+      <c r="F1" s="12"/>
       <c r="G1" s="13"/>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="14"/>
+      <c r="I1" s="12"/>
       <c r="J1" s="13"/>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="14"/>
+      <c r="L1" s="12"/>
       <c r="M1" s="13"/>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
       <c r="S1" s="13"/>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="8"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="7"/>
     </row>
-    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -752,21 +757,28 @@
       <c r="S2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="Q3" s="2">
         <f xml:space="preserve"> N3+O3+P3</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>

--- a/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480C1379-988C-4729-9DFC-5CCF7BC3CF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323FA1AA-4B2D-4981-9E34-E41B887FD0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -65,28 +65,15 @@
     <t>天气影响</t>
   </si>
   <si>
-    <t>主机日耗</t>
-  </si>
-  <si>
-    <t>泵机日耗</t>
-  </si>
-  <si>
     <t>柴油补充</t>
   </si>
   <si>
     <t>柴油库存</t>
   </si>
   <si>
-    <t>滑油日耗</t>
-  </si>
-  <si>
     <t>简要说明</t>
   </si>
   <si>
-    <t>辅机日耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>其他停工</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,10 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>淡水日耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>淡水补充</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,15 +110,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>柴油总日耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>滑油补充</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>滑油库存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辅机消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泵机消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油总消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -323,6 +326,9 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -330,9 +336,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -654,7 +657,7 @@
   <cols>
     <col min="1" max="1" width="10.625" style="6"/>
     <col min="2" max="4" width="10.625" style="2"/>
-    <col min="5" max="10" width="10.625" style="14"/>
+    <col min="5" max="10" width="10.625" style="11"/>
     <col min="11" max="16" width="10.625" style="2"/>
     <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
     <col min="18" max="22" width="10.625" style="2"/>
@@ -665,38 +668,38 @@
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="7"/>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="13"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="13"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="11" t="s">
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="U1" s="12"/>
-      <c r="V1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="14"/>
       <c r="W1" s="7"/>
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -728,46 +731,46 @@
         <v>8</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="W2" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">

--- a/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（001）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323FA1AA-4B2D-4981-9E34-E41B887FD0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1629D3C5-AD10-480C-91EA-037A10BAD953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>日期</t>
   </si>
@@ -47,98 +47,103 @@
     <t>船次</t>
   </si>
   <si>
+    <t>施工准备</t>
+  </si>
+  <si>
+    <t>挖泥时间</t>
+  </si>
+  <si>
+    <t>航行时间</t>
+  </si>
+  <si>
+    <t>检修时间</t>
+  </si>
+  <si>
+    <t>天气影响</t>
+  </si>
+  <si>
+    <t>柴油补充</t>
+  </si>
+  <si>
+    <t>柴油库存</t>
+  </si>
+  <si>
+    <t>简要说明</t>
+  </si>
+  <si>
+    <t>其他停工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停工时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水库存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油库存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辅机消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泵机消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油总消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>船方</t>
-  </si>
-  <si>
-    <t>施工准备</t>
-  </si>
-  <si>
-    <t>挖泥时间</t>
-  </si>
-  <si>
-    <t>航行时间</t>
-  </si>
-  <si>
-    <t>检修时间</t>
-  </si>
-  <si>
-    <t>天气影响</t>
-  </si>
-  <si>
-    <t>柴油补充</t>
-  </si>
-  <si>
-    <t>柴油库存</t>
-  </si>
-  <si>
-    <t>简要说明</t>
-  </si>
-  <si>
-    <t>其他停工</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>施工时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停工时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水（吨）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>柴油（吨）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水补充</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水库存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油（吨）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油补充</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油库存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辅机消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>泵机消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>柴油总消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作业量（万元）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -286,7 +291,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -337,6 +342,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -356,9 +365,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -396,7 +405,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -502,7 +511,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -644,7 +653,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -652,57 +661,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B800CC8-A909-447B-A086-099E135E3E25}">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="6"/>
     <col min="2" max="4" width="10.625" style="2"/>
-    <col min="5" max="10" width="10.625" style="11"/>
-    <col min="11" max="16" width="10.625" style="2"/>
-    <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
-    <col min="18" max="22" width="10.625" style="2"/>
-    <col min="23" max="23" width="20.625" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="10.625" style="2"/>
+    <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
+    <col min="6" max="11" width="10.625" style="11"/>
+    <col min="12" max="17" width="10.625" style="2"/>
+    <col min="18" max="18" width="12.625" style="2" customWidth="1"/>
+    <col min="19" max="23" width="10.625" style="2"/>
+    <col min="24" max="24" width="20.625" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="7"/>
       <c r="C1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="12" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="12" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="12" t="s">
+      <c r="M1" s="13"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="13"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="13"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="7"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="13"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="7"/>
     </row>
-    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -712,81 +723,84 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="T2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="4" t="s">
+      <c r="V2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="Q3" s="2">
-        <f xml:space="preserve"> N3+O3+P3</f>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R3" s="2">
+        <f xml:space="preserve"> O3+P3+Q3</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:T1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
